--- a/supplementary_results.xlsx
+++ b/supplementary_results.xlsx
@@ -481,7 +481,7 @@
       <t xml:space="preserve">
 The reviewer raises a concern that the layer-wise design may be heuristic. 
 In addition to the layer-wise ablation study in the original paper, we further conduct a more comprehensive layer sensitivity analysis. 
-Specifically, PSII assigns an Optimal Layer Configuration (OLC) to each persona variable, categorizing them into low-, mid-, and high-level injection layers based on empirical performance. 
+Specifically, PSII assigns an Optimal Layer Configuration (OLC) to each persona variable, categorizing them into low-, mid-, and high-level injection layers. 
 To validate the effectiveness of this design, we perform controlled experiments on Qwen-2.5-7B (28 layers) with the following settings: 
 (1) Randomly assigning injection layers for each persona variable (two independent runs);
 (2) Shifting all OLC layers by +2/-2;
@@ -698,7 +698,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -821,12 +821,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -845,12 +839,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -864,12 +852,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1120,49 +1102,49 @@
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
